--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92230</v>
+        <v>92233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92230</v>
+        <v>92233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92230</v>
+        <v>92233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92230</v>
+        <v>92233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92230</v>
+        <v>92233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136019207</v>
       </c>
       <c r="B4" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136019225</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136019227</v>
       </c>
       <c r="B9" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136019228</v>
       </c>
       <c r="B10" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136019229</v>
       </c>
       <c r="B11" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136019230</v>
       </c>
       <c r="B12" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136019231</v>
       </c>
       <c r="B32" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136019232</v>
       </c>
       <c r="B33" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>136019233</v>
       </c>
       <c r="B34" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136019234</v>
       </c>
       <c r="B35" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>136019235</v>
       </c>
       <c r="B36" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>136019236</v>
       </c>
       <c r="B37" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136019217</v>
       </c>
       <c r="B38" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>136019219</v>
       </c>
       <c r="B39" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>136019220</v>
       </c>
       <c r="B40" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>136019221</v>
       </c>
       <c r="B41" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>136019222</v>
       </c>
       <c r="B42" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,32 +1815,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136019238</v>
+        <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>79474</v>
+        <v>93437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>854410</v>
+        <v>854373</v>
       </c>
       <c r="R13" t="n">
-        <v>7478891</v>
+        <v>7479091</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1911,54 +1911,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019238</t>
+          <t>https://artportalen.se/Sighting/136866918</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124427404</v>
+        <v>136019238</v>
       </c>
       <c r="B14" t="n">
-        <v>80367</v>
+        <v>79474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>854289</v>
+        <v>854410</v>
       </c>
       <c r="R14" t="n">
-        <v>7479238</v>
+        <v>7478891</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2013,51 +2013,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427404</t>
+          <t>https://artportalen.se/Sighting/136019238</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134119760</v>
+        <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>80493</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>854328</v>
+        <v>854401</v>
       </c>
       <c r="R15" t="n">
-        <v>7479069</v>
+        <v>7478903</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2115,16 +2115,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119760</t>
+          <t>https://artportalen.se/Sighting/136866905</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134119761</v>
+        <v>124427404</v>
       </c>
       <c r="B16" t="n">
-        <v>80493</v>
+        <v>80367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>854332</v>
+        <v>854289</v>
       </c>
       <c r="R16" t="n">
-        <v>7479065</v>
+        <v>7479238</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2186,12 +2186,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2217,13 +2217,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119761</t>
+          <t>https://artportalen.se/Sighting/124427404</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134119777</v>
+        <v>134119760</v>
       </c>
       <c r="B17" t="n">
         <v>80493</v>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>854404</v>
+        <v>854328</v>
       </c>
       <c r="R17" t="n">
-        <v>7478864</v>
+        <v>7479069</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2319,16 +2319,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119777</t>
+          <t>https://artportalen.se/Sighting/134119760</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136019214</v>
+        <v>134119761</v>
       </c>
       <c r="B18" t="n">
-        <v>80594</v>
+        <v>80493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,14 +2356,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lammivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>854350</v>
+        <v>854332</v>
       </c>
       <c r="R18" t="n">
-        <v>7479038</v>
+        <v>7479065</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,16 +2421,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019214</t>
+          <t>https://artportalen.se/Sighting/134119761</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136019215</v>
+        <v>134119777</v>
       </c>
       <c r="B19" t="n">
-        <v>80594</v>
+        <v>80493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,14 +2458,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lammivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>854344</v>
+        <v>854404</v>
       </c>
       <c r="R19" t="n">
-        <v>7479046</v>
+        <v>7478864</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2523,13 +2523,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019215</t>
+          <t>https://artportalen.se/Sighting/134119777</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136019216</v>
+        <v>136019214</v>
       </c>
       <c r="B20" t="n">
         <v>80594</v>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>854339</v>
+        <v>854350</v>
       </c>
       <c r="R20" t="n">
-        <v>7479128</v>
+        <v>7479038</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2625,16 +2625,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019216</t>
+          <t>https://artportalen.se/Sighting/136019214</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124427409</v>
+        <v>136019215</v>
       </c>
       <c r="B21" t="n">
-        <v>80467</v>
+        <v>80594</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2642,37 +2642,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>854407</v>
+        <v>854344</v>
       </c>
       <c r="R21" t="n">
-        <v>7478920</v>
+        <v>7479046</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2727,16 +2727,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427409</t>
+          <t>https://artportalen.se/Sighting/136019215</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124427377</v>
+        <v>136019216</v>
       </c>
       <c r="B22" t="n">
-        <v>80468</v>
+        <v>80594</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,37 +2744,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>854407</v>
+        <v>854339</v>
       </c>
       <c r="R22" t="n">
-        <v>7478920</v>
+        <v>7479128</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2829,16 +2829,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427377</t>
+          <t>https://artportalen.se/Sighting/136019216</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124427378</v>
+        <v>124427409</v>
       </c>
       <c r="B23" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>854414</v>
+        <v>854407</v>
       </c>
       <c r="R23" t="n">
-        <v>7478861</v>
+        <v>7478920</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,16 +2931,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427378</t>
+          <t>https://artportalen.se/Sighting/124427409</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136019224</v>
+        <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>854344</v>
+        <v>854429</v>
       </c>
       <c r="R24" t="n">
-        <v>7479046</v>
+        <v>7478863</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3033,16 +3033,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019224</t>
+          <t>https://artportalen.se/Sighting/136866960</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124855305</v>
+        <v>124427377</v>
       </c>
       <c r="B25" t="n">
-        <v>57950</v>
+        <v>80468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,34 +3050,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>854281</v>
+        <v>854407</v>
       </c>
       <c r="R25" t="n">
-        <v>7479174</v>
+        <v>7478920</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3135,54 +3135,54 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855305</t>
+          <t>https://artportalen.se/Sighting/124427377</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136019209</v>
+        <v>124427378</v>
       </c>
       <c r="B26" t="n">
-        <v>58006</v>
+        <v>80468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lammivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>854390</v>
+        <v>854414</v>
       </c>
       <c r="R26" t="n">
-        <v>7478982</v>
+        <v>7478861</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3206,17 +3206,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre födosök  i form av avbarkad klen gran 2-4 år gammal. .</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3242,38 +3237,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019209</t>
+          <t>https://artportalen.se/Sighting/124427378</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136019210</v>
+        <v>136019224</v>
       </c>
       <c r="B27" t="n">
-        <v>58006</v>
+        <v>80601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3283,10 +3278,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>854383</v>
+        <v>854344</v>
       </c>
       <c r="R27" t="n">
-        <v>7478979</v>
+        <v>7479046</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3321,16 +3316,11 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran. Kan antas vara gjorda av tretåig hackspett då arten förekommer i området och andra födosök noterats i närheten.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3349,55 +3339,51 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019210</t>
+          <t>https://artportalen.se/Sighting/136019224</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136019211</v>
+        <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>58006</v>
+        <v>80603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>854357</v>
+        <v>854429</v>
       </c>
       <c r="R28" t="n">
-        <v>7479039</v>
+        <v>7478863</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3424,17 +3410,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Avbarkad klen gran. 2-3 år gammalt.</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3460,33 +3441,33 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019211</t>
+          <t>https://artportalen.se/Sighting/136866935</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136019212</v>
+        <v>124855305</v>
       </c>
       <c r="B29" t="n">
-        <v>58006</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3495,23 +3476,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lammivaara, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>854353</v>
+        <v>854281</v>
       </c>
       <c r="R29" t="n">
-        <v>7479064</v>
+        <v>7479174</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3535,17 +3512,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Avbarkad klen gran. Antagligen födosök vintertid.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3571,33 +3543,33 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019212</t>
+          <t>https://artportalen.se/Sighting/124855305</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134119852</v>
+        <v>136019209</v>
       </c>
       <c r="B30" t="n">
-        <v>57153</v>
+        <v>58006</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3608,14 +3580,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>854326</v>
+        <v>854390</v>
       </c>
       <c r="R30" t="n">
-        <v>7479083</v>
+        <v>7478982</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3642,12 +3614,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre födosök  i form av avbarkad klen gran 2-4 år gammal. .</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3673,33 +3650,33 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119852</t>
+          <t>https://artportalen.se/Sighting/136019209</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136019237</v>
+        <v>136019210</v>
       </c>
       <c r="B31" t="n">
-        <v>57184</v>
+        <v>58006</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3714,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>854439</v>
+        <v>854383</v>
       </c>
       <c r="R31" t="n">
-        <v>7478865</v>
+        <v>7478979</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3752,11 +3729,16 @@
           <t>2026-08-16</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran. Kan antas vara gjorda av tretåig hackspett då arten förekommer i området och andra födosök noterats i närheten.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG31" t="b">
         <v>0</v>
@@ -3775,44 +3757,44 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019237</t>
+          <t>https://artportalen.se/Sighting/136019210</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136019231</v>
+        <v>136019211</v>
       </c>
       <c r="B32" t="n">
-        <v>99346</v>
+        <v>58006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3820,10 +3802,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>854370</v>
+        <v>854357</v>
       </c>
       <c r="R32" t="n">
-        <v>7479029</v>
+        <v>7479039</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3860,7 +3842,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>Avbarkad klen gran. 2-3 år gammalt.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3869,7 +3851,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3887,48 +3868,44 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019231</t>
+          <t>https://artportalen.se/Sighting/136019211</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136019232</v>
+        <v>136019212</v>
       </c>
       <c r="B33" t="n">
-        <v>99346</v>
+        <v>58006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3936,10 +3913,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>854443</v>
+        <v>854353</v>
       </c>
       <c r="R33" t="n">
-        <v>7478887</v>
+        <v>7479064</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3974,13 +3951,17 @@
           <t>2026-08-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran. Antagligen födosök vintertid.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3998,59 +3979,51 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019232</t>
+          <t>https://artportalen.se/Sighting/136019212</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136019233</v>
+        <v>134119852</v>
       </c>
       <c r="B34" t="n">
-        <v>99346</v>
+        <v>57153</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lammivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>854407</v>
+        <v>854326</v>
       </c>
       <c r="R34" t="n">
-        <v>7478891</v>
+        <v>7479083</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4077,12 +4050,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4091,7 +4064,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4109,59 +4081,51 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019233</t>
+          <t>https://artportalen.se/Sighting/134119852</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136019234</v>
+        <v>136019237</v>
       </c>
       <c r="B35" t="n">
-        <v>99346</v>
+        <v>57184</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>854374</v>
+        <v>854439</v>
       </c>
       <c r="R35" t="n">
-        <v>7478990</v>
+        <v>7478865</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4202,7 +4166,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4220,55 +4183,51 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019234</t>
+          <t>https://artportalen.se/Sighting/136019237</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136019235</v>
+        <v>136866890</v>
       </c>
       <c r="B36" t="n">
-        <v>99346</v>
+        <v>58169</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854386</v>
+        <v>854402</v>
       </c>
       <c r="R36" t="n">
-        <v>7479026</v>
+        <v>7478897</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4295,12 +4254,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4309,7 +4268,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4327,59 +4285,51 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019235</t>
+          <t>https://artportalen.se/Sighting/136866890</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136019236</v>
+        <v>136866891</v>
       </c>
       <c r="B37" t="n">
-        <v>99346</v>
+        <v>58169</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854377</v>
+        <v>854369</v>
       </c>
       <c r="R37" t="n">
-        <v>7479027</v>
+        <v>7478971</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4406,12 +4356,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4420,7 +4370,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4438,51 +4387,55 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019236</t>
+          <t>https://artportalen.se/Sighting/136866891</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136019217</v>
+        <v>136019231</v>
       </c>
       <c r="B38" t="n">
-        <v>99368</v>
+        <v>99346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>854379</v>
+        <v>854370</v>
       </c>
       <c r="R38" t="n">
-        <v>7479010</v>
+        <v>7479029</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4517,12 +4470,18 @@
           <t>2026-08-16</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4540,51 +4499,59 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019217</t>
+          <t>https://artportalen.se/Sighting/136019231</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136019219</v>
+        <v>136019232</v>
       </c>
       <c r="B39" t="n">
-        <v>99368</v>
+        <v>99346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854352</v>
+        <v>854443</v>
       </c>
       <c r="R39" t="n">
-        <v>7479021</v>
+        <v>7478887</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4625,6 +4592,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4642,51 +4610,59 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019219</t>
+          <t>https://artportalen.se/Sighting/136019232</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136019220</v>
+        <v>136019233</v>
       </c>
       <c r="B40" t="n">
-        <v>99368</v>
+        <v>99346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854363</v>
+        <v>854407</v>
       </c>
       <c r="R40" t="n">
-        <v>7479028</v>
+        <v>7478891</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4727,6 +4703,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4744,51 +4721,59 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019220</t>
+          <t>https://artportalen.se/Sighting/136019233</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136019221</v>
+        <v>136019234</v>
       </c>
       <c r="B41" t="n">
-        <v>99368</v>
+        <v>99346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854363</v>
+        <v>854374</v>
       </c>
       <c r="R41" t="n">
-        <v>7479038</v>
+        <v>7478990</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4829,6 +4814,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4846,51 +4832,55 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019221</t>
+          <t>https://artportalen.se/Sighting/136019234</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136019222</v>
+        <v>136019235</v>
       </c>
       <c r="B42" t="n">
-        <v>99368</v>
+        <v>99346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>854342</v>
+        <v>854386</v>
       </c>
       <c r="R42" t="n">
-        <v>7479060</v>
+        <v>7479026</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4931,6 +4921,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4947,6 +4938,1443 @@
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019235</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136019236</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99346</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>854377</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7479027</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019236</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136866898</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>854404</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7478910</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866898</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136866899</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>854398</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7478941</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866899</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136866900</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>854386</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7478964</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866900</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136866901</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>854372</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7478969</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866901</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136866902</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>854367</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7478972</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866902</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136866903</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>854333</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7479067</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866903</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136866904</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>854415</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7478911</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866904</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136866894</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98221</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>854370</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7479102</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866894</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136019217</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>854379</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7479010</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019217</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136019219</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>854352</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7479021</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019219</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136019220</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>854363</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7479028</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019220</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136019221</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>854363</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7479038</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019221</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136019222</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>854342</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7479060</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136019222</t>
         </is>
@@ -4995,6 +6423,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3985,27 +3985,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134119852</v>
+        <v>136866888</v>
       </c>
       <c r="B34" t="n">
-        <v>57153</v>
+        <v>58008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4016,14 +4016,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>854326</v>
+        <v>854394</v>
       </c>
       <c r="R34" t="n">
-        <v>7479083</v>
+        <v>7478892</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4050,12 +4050,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre födosök, klen avbarkad gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4081,33 +4086,33 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119852</t>
+          <t>https://artportalen.se/Sighting/136866888</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136019237</v>
+        <v>136866889</v>
       </c>
       <c r="B35" t="n">
-        <v>57184</v>
+        <v>58008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4116,16 +4121,20 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>854439</v>
+        <v>854347</v>
       </c>
       <c r="R35" t="n">
-        <v>7478865</v>
+        <v>7479057</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4152,19 +4161,24 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran. Mest troligt  födosök av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
@@ -4180,54 +4194,58 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Projekt tretåig hackspett östra Norrbotten</t>
+        </is>
+      </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019237</t>
+          <t>https://artportalen.se/Sighting/136866889</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136866890</v>
+        <v>134119852</v>
       </c>
       <c r="B36" t="n">
-        <v>58169</v>
+        <v>57153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lammivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854402</v>
+        <v>854326</v>
       </c>
       <c r="R36" t="n">
-        <v>7478897</v>
+        <v>7479083</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4254,12 +4272,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4285,38 +4303,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866890</t>
+          <t>https://artportalen.se/Sighting/134119852</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136866891</v>
+        <v>136019237</v>
       </c>
       <c r="B37" t="n">
-        <v>58169</v>
+        <v>57184</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4326,10 +4344,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854369</v>
+        <v>854439</v>
       </c>
       <c r="R37" t="n">
-        <v>7478971</v>
+        <v>7478865</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4356,12 +4374,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4387,55 +4405,51 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866891</t>
+          <t>https://artportalen.se/Sighting/136019237</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136019231</v>
+        <v>136866890</v>
       </c>
       <c r="B38" t="n">
-        <v>99346</v>
+        <v>58169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>854370</v>
+        <v>854402</v>
       </c>
       <c r="R38" t="n">
-        <v>7479029</v>
+        <v>7478897</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4462,17 +4476,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>10 bladrosetter</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4481,7 +4490,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4499,59 +4507,51 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019231</t>
+          <t>https://artportalen.se/Sighting/136866890</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136019232</v>
+        <v>136866891</v>
       </c>
       <c r="B39" t="n">
-        <v>99346</v>
+        <v>58169</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854443</v>
+        <v>854369</v>
       </c>
       <c r="R39" t="n">
-        <v>7478887</v>
+        <v>7478971</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4578,12 +4578,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4592,7 +4592,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4610,48 +4609,48 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019232</t>
+          <t>https://artportalen.se/Sighting/136866891</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136019233</v>
+        <v>136866896</v>
       </c>
       <c r="B40" t="n">
-        <v>99346</v>
+        <v>58112</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4659,10 +4658,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854407</v>
+        <v>854392</v>
       </c>
       <c r="R40" t="n">
-        <v>7478891</v>
+        <v>7479013</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4689,12 +4688,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Två individer.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4703,7 +4707,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4718,16 +4721,20 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Projekt tretåig hackspett östra Norrbotten</t>
+        </is>
+      </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019233</t>
+          <t>https://artportalen.se/Sighting/136866896</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136019234</v>
+        <v>136019231</v>
       </c>
       <c r="B41" t="n">
         <v>99346</v>
@@ -4757,11 +4764,7 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4770,10 +4773,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854374</v>
+        <v>854370</v>
       </c>
       <c r="R41" t="n">
-        <v>7478990</v>
+        <v>7479029</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4808,6 +4811,11 @@
           <t>2026-08-16</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4832,13 +4840,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019234</t>
+          <t>https://artportalen.se/Sighting/136019231</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136019235</v>
+        <v>136019232</v>
       </c>
       <c r="B42" t="n">
         <v>99346</v>
@@ -4868,7 +4876,11 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4877,10 +4889,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>854386</v>
+        <v>854443</v>
       </c>
       <c r="R42" t="n">
-        <v>7479026</v>
+        <v>7478887</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4939,13 +4951,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019235</t>
+          <t>https://artportalen.se/Sighting/136019232</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136019236</v>
+        <v>136019233</v>
       </c>
       <c r="B43" t="n">
         <v>99346</v>
@@ -4988,10 +5000,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854377</v>
+        <v>854407</v>
       </c>
       <c r="R43" t="n">
-        <v>7479027</v>
+        <v>7478891</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5050,16 +5062,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019236</t>
+          <t>https://artportalen.se/Sighting/136019233</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136866898</v>
+        <v>136019234</v>
       </c>
       <c r="B44" t="n">
-        <v>99353</v>
+        <v>99346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5085,16 +5097,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>854404</v>
+        <v>854374</v>
       </c>
       <c r="R44" t="n">
-        <v>7478910</v>
+        <v>7478990</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5121,12 +5141,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5135,6 +5155,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5152,16 +5173,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866898</t>
+          <t>https://artportalen.se/Sighting/136019234</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136866899</v>
+        <v>136019235</v>
       </c>
       <c r="B45" t="n">
-        <v>99353</v>
+        <v>99346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5187,16 +5208,20 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>854398</v>
+        <v>854386</v>
       </c>
       <c r="R45" t="n">
-        <v>7478941</v>
+        <v>7479026</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5223,12 +5248,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5237,6 +5262,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5254,16 +5280,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866899</t>
+          <t>https://artportalen.se/Sighting/136019235</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136866900</v>
+        <v>136019236</v>
       </c>
       <c r="B46" t="n">
-        <v>99353</v>
+        <v>99346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5289,16 +5315,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854386</v>
+        <v>854377</v>
       </c>
       <c r="R46" t="n">
-        <v>7478964</v>
+        <v>7479027</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5325,12 +5359,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5339,6 +5373,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5356,13 +5391,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866900</t>
+          <t>https://artportalen.se/Sighting/136019236</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136866901</v>
+        <v>136866898</v>
       </c>
       <c r="B47" t="n">
         <v>99353</v>
@@ -5397,10 +5432,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854372</v>
+        <v>854404</v>
       </c>
       <c r="R47" t="n">
-        <v>7478969</v>
+        <v>7478910</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5458,13 +5493,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866901</t>
+          <t>https://artportalen.se/Sighting/136866898</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136866902</v>
+        <v>136866899</v>
       </c>
       <c r="B48" t="n">
         <v>99353</v>
@@ -5499,10 +5534,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854367</v>
+        <v>854398</v>
       </c>
       <c r="R48" t="n">
-        <v>7478972</v>
+        <v>7478941</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5560,13 +5595,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866902</t>
+          <t>https://artportalen.se/Sighting/136866899</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136866903</v>
+        <v>136866900</v>
       </c>
       <c r="B49" t="n">
         <v>99353</v>
@@ -5601,10 +5636,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854333</v>
+        <v>854386</v>
       </c>
       <c r="R49" t="n">
-        <v>7479067</v>
+        <v>7478964</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5662,13 +5697,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866903</t>
+          <t>https://artportalen.se/Sighting/136866900</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136866904</v>
+        <v>136866901</v>
       </c>
       <c r="B50" t="n">
         <v>99353</v>
@@ -5703,10 +5738,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>854415</v>
+        <v>854372</v>
       </c>
       <c r="R50" t="n">
-        <v>7478911</v>
+        <v>7478969</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5764,38 +5799,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866904</t>
+          <t>https://artportalen.se/Sighting/136866901</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136866894</v>
+        <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>98221</v>
+        <v>99353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5805,10 +5840,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>854370</v>
+        <v>854367</v>
       </c>
       <c r="R51" t="n">
-        <v>7479102</v>
+        <v>7478972</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5866,38 +5901,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866894</t>
+          <t>https://artportalen.se/Sighting/136866902</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136019217</v>
+        <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99368</v>
+        <v>99353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5907,10 +5942,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854379</v>
+        <v>854333</v>
       </c>
       <c r="R52" t="n">
-        <v>7479010</v>
+        <v>7479067</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5937,12 +5972,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5968,38 +6003,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019217</t>
+          <t>https://artportalen.se/Sighting/136866903</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136019219</v>
+        <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99368</v>
+        <v>99353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6009,10 +6044,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>854352</v>
+        <v>854415</v>
       </c>
       <c r="R53" t="n">
-        <v>7479021</v>
+        <v>7478911</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6039,12 +6074,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6070,16 +6105,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019219</t>
+          <t>https://artportalen.se/Sighting/136866904</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136019220</v>
+        <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>99368</v>
+        <v>98221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6087,21 +6122,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6111,10 +6146,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854363</v>
+        <v>854370</v>
       </c>
       <c r="R54" t="n">
-        <v>7479028</v>
+        <v>7479102</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6141,12 +6176,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6172,13 +6207,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019220</t>
+          <t>https://artportalen.se/Sighting/136866894</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136019221</v>
+        <v>136019217</v>
       </c>
       <c r="B55" t="n">
         <v>99368</v>
@@ -6213,10 +6248,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854363</v>
+        <v>854379</v>
       </c>
       <c r="R55" t="n">
-        <v>7479038</v>
+        <v>7479010</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6274,13 +6309,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136019221</t>
+          <t>https://artportalen.se/Sighting/136019217</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136019222</v>
+        <v>136019219</v>
       </c>
       <c r="B56" t="n">
         <v>99368</v>
@@ -6315,10 +6350,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854342</v>
+        <v>854352</v>
       </c>
       <c r="R56" t="n">
-        <v>7479060</v>
+        <v>7479021</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6375,6 +6410,312 @@
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019219</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136019220</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>854363</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7479028</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019220</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136019221</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>854363</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7479038</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136019221</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136019222</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>854342</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7479060</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136019222</t>
         </is>
@@ -6437,6 +6778,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>136866888</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>136866889</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>136866890</v>
       </c>
       <c r="B38" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866891</v>
       </c>
       <c r="B39" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>136866896</v>
       </c>
       <c r="B40" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>136866888</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>136866889</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>136866890</v>
       </c>
       <c r="B38" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866891</v>
       </c>
       <c r="B39" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>136866896</v>
       </c>
       <c r="B40" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>136866888</v>
       </c>
       <c r="B34" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>136866889</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>136866890</v>
       </c>
       <c r="B38" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866891</v>
       </c>
       <c r="B39" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>136866896</v>
       </c>
       <c r="B40" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>136866888</v>
       </c>
       <c r="B34" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>136866889</v>
       </c>
       <c r="B35" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>136866890</v>
       </c>
       <c r="B38" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866891</v>
       </c>
       <c r="B39" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>136866896</v>
       </c>
       <c r="B40" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>136866888</v>
       </c>
       <c r="B34" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>136866889</v>
       </c>
       <c r="B35" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>136866890</v>
       </c>
       <c r="B38" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136866891</v>
       </c>
       <c r="B39" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>136866896</v>
       </c>
       <c r="B40" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>136866918</v>
       </c>
       <c r="B13" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>136866905</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>136866960</v>
       </c>
       <c r="B24" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136866935</v>
       </c>
       <c r="B28" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>136866898</v>
       </c>
       <c r="B47" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136866899</v>
       </c>
       <c r="B48" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>136866900</v>
       </c>
       <c r="B49" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>136866901</v>
       </c>
       <c r="B50" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>136866902</v>
       </c>
       <c r="B51" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>136866903</v>
       </c>
       <c r="B52" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136866904</v>
       </c>
       <c r="B53" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>136866894</v>
       </c>
       <c r="B54" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 28528-2026 artfynd.xlsx
+++ b/artfynd/A 28528-2026 artfynd.xlsx
@@ -3988,7 +3988,7 @@
         <v>136866888</v>
       </c>
       <c r="B34" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>136866889</v>
       </c>
       <c r="B35" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>136866896</v>
       </c>
       <c r="B40" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
